--- a/TC Telnyx.xlsx
+++ b/TC Telnyx.xlsx
@@ -12,7 +12,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="X+od69/yl+exEm2ywPnxrJXpjfPhtAaRXIESsxTlza8="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="PhpsOzo2n7e+CwtKnSkl9yn9YemCpL2JG9rzP4HmMaM="/>
     </ext>
   </extLst>
 </workbook>
@@ -274,26 +274,20 @@
     <t>TC-09</t>
   </si>
   <si>
-    <t>Developer Docs Page &amp; Navigation</t>
+    <t>Search the Developer Portal</t>
   </si>
   <si>
     <t>Developer Docs</t>
   </si>
   <si>
-    <t>1. Navigate to https://developers.telnyx.com
-2. Verify page title
-3. Verify "Development" section exists
-4. Verify search functionality
-5. Verify navigation links
-6. Verify community links</t>
-  </si>
-  <si>
-    <t>1. Docs page loads
-2. Title is not empty
-3. "Development" text present
-4. Search bar or search button exists
-5. Links to /development exist
-6. GitHub link (github.com/team-telnyx) exists</t>
+    <t>1. Go to developers.telnyx.com.
+2. Enter ""Send a message"" in the search field.
+3. Press Enter.</t>
+  </si>
+  <si>
+    <t>1. Page loads
+2. The results appear relevant to the query "Send a message"
+3. The URL contains the search parameters.</t>
   </si>
   <si>
     <t>cypress/e2e/docs.cy.js</t>
@@ -420,7 +414,6 @@
       <sz val="11.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -431,13 +424,11 @@
       <b/>
       <color rgb="FF006600"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0070C0"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -449,12 +440,10 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -509,7 +498,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -544,18 +533,21 @@
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" readingOrder="1" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" readingOrder="1" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="1" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="4" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment horizontal="left" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1168,7 +1160,7 @@
       <c r="A10" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="14" t="s">
         <v>57</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -1177,10 +1169,10 @@
       <c r="D10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="14" t="s">
         <v>60</v>
       </c>
       <c r="G10" s="3" t="s">
@@ -2250,134 +2242,134 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="25.0"/>
     <col customWidth="1" min="2" max="2" width="50.0"/>
-    <col customWidth="1" min="3" max="26" width="8.71"/>
+    <col customWidth="1" min="3" max="22" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14"/>
-      <c r="W1" s="14"/>
-      <c r="X1" s="14"/>
-      <c r="Y1" s="14"/>
-      <c r="Z1" s="14"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="16" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="17" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="17" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="16" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="16" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="16" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="16" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="16" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="16" t="s">
         <v>92</v>
       </c>
     </row>

--- a/TC Telnyx.xlsx
+++ b/TC Telnyx.xlsx
@@ -59,7 +59,7 @@
   <si>
     <t>1. Navigate to https://telnyx.com
 2. Check page title
-3. Check main heading (h1)
+3. Check main heading
 4. Check meta description tag</t>
   </si>
   <si>
@@ -88,17 +88,15 @@
   </si>
   <si>
     <t>1. Navigate to https://telnyx.com
-2. Accept cookie consent
-3. Hover over "Products" menu in header
-4. Click "Voice API" link in dropdown
-5. Verify URL</t>
+2. Hover over "Products" menu in header
+3. Click "Voice API" link in dropdown
+4. Verify URL</t>
   </si>
   <si>
     <t>1. Page loads
-2. Banner dismissed
-3. Dropdown menu appears
-4. Navigates to /products/voice-api
-5. URL contains /products/voice-api</t>
+2. Dropdown menu appears
+3. Navigates to /products/voice-api
+4. URL contains /products/voice-api</t>
   </si>
   <si>
     <t>cypress/e2e/navigation.cy.js</t>
@@ -144,14 +142,14 @@
   <si>
     <t>1. Navigate to https://portal.telnyx.com/
 2. Wait for email input to be visible
-3. Click sign-in button without entering email
+3. Click "Send me sign-in link" button without entering email
 4. Verify error state</t>
   </si>
   <si>
     <t>1. Login page loads
 2. Login form is rendered
-3. Button clicked
-4. Error message about required/invalid email appears OR user stays on login page</t>
+3. Button is clickable
+4. Error message about required/invalid email appears, user stays on login page</t>
   </si>
   <si>
     <t>TC-05</t>
@@ -161,28 +159,6 @@
   </si>
   <si>
     <t>Pricing</t>
-  </si>
-  <si>
-    <t>1. Navigate to https://telnyx.com/pricing/messaging
-2. Verify pricing content
-3. Change country from US to UK
-6. Verify pricing change</t>
-  </si>
-  <si>
-    <t>1. Page loads
-2. Title contains "Pricing"
-3. Dollar signs ($) or pricing text present for US
-4. It is possible to change country
-5. Pricing is changed for UK</t>
-  </si>
-  <si>
-    <t>cypress/e2e/pricing.cy.js</t>
-  </si>
-  <si>
-    <t>TC-06</t>
-  </si>
-  <si>
-    <t>Currency change in the calculator</t>
   </si>
   <si>
     <r>
@@ -200,6 +176,51 @@
         <sz val="11.0"/>
         <u/>
       </rPr>
+      <t>https://telnyx.com/pricing/messaging</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color theme="1"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t xml:space="preserve">
+2. Change country from US to UK
+3. Verify pricing change</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Page loads
+2. Pricing text present for US
+3. It is possible to change country
+4. Pricing is changed for UK
+5. Page heading is visible and title contains "Pricing"
+6. Previous US pricing is no longer shown after country change</t>
+  </si>
+  <si>
+    <t>cypress/e2e/pricing.cy.js</t>
+  </si>
+  <si>
+    <t>TC-06</t>
+  </si>
+  <si>
+    <t>Currency change in the calculator</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color theme="1"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t xml:space="preserve">1. Navigate to </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color rgb="FF1155CC"/>
+        <sz val="11.0"/>
+      </rPr>
       <t>https://telnyx.com/pricing/elastic-sip</t>
     </r>
     <r>
@@ -209,17 +230,19 @@
         <sz val="11.0"/>
       </rPr>
       <t xml:space="preserve">
-2. Verify pricing content
-3. Change country from USD to EUR
-4. Verify pricing data</t>
+2. Change country from USD to EUR
+3. Verify pricing data</t>
     </r>
   </si>
   <si>
-    <t>1. Page loads
-2. Title contains "Pricing"
-3. Dollar signs ($) present for USD
-4. It is possible to change currency
-5. Euro signs (€) present for EUR</t>
+    <t xml:space="preserve">1. Page loads
+2. Dollar signs ($) present for USD price
+3. It is possible to change currency
+4. Euro signs (€) present for EUR price
+5. Page heading is visible and title contains "SIP"
+6. "Pay as you go" pricing tier is visible
+7. "Volume-based" pricing tier is visible
+</t>
   </si>
   <si>
     <t>TC-07</t>
@@ -231,11 +254,35 @@
     <t>Compliance</t>
   </si>
   <si>
-    <t>1. Navigate to https://telnyx.com
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color theme="1"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t xml:space="preserve">1. Navigate to </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color rgb="FF1155CC"/>
+        <sz val="11.0"/>
+        <u/>
+      </rPr>
+      <t>https://telnyx.com</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color theme="1"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t xml:space="preserve">
 2. Verify cookie banner appears
 3. Click "Accept All Cookies" button
 4. Verify banner disappears
 5. Verify cookie is set</t>
+    </r>
   </si>
   <si>
     <t>1. Page loads
@@ -281,13 +328,17 @@
   </si>
   <si>
     <t>1. Go to developers.telnyx.com.
-2. Enter ""Send a message"" in the search field.
-3. Press Enter.</t>
-  </si>
-  <si>
-    <t>1. Page loads
+2. Enter "Send a message" in the search field.
+3. Сlick first searched result.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Page loads
 2. The results appear relevant to the query "Send a message"
-3. The URL contains the search parameters.</t>
+3. The URL contains the search parameters.
+4. Search dialog closes after clicking the result
+5. Page navigates to a documentation article
+6. The destination page has a visible heading
+</t>
   </si>
   <si>
     <t>cypress/e2e/docs.cy.js</t>
@@ -302,22 +353,44 @@
     <t>Responsiveness</t>
   </si>
   <si>
-    <t>1. Set viewport to 375×812
-2. Navigate to https://telnyx.com
-3. Accept cookie consent
-4. Click hamburger menu button
-5. Verify menu opens
-6. Verify "Products" link
-7. Verify "Solutions" link</t>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color theme="1"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t xml:space="preserve">1. Set viewport to 375×812
+2. Navigate to </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color rgb="FF1155CC"/>
+        <sz val="11.0"/>
+        <u/>
+      </rPr>
+      <t>https://telnyx.com</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color theme="1"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t xml:space="preserve">
+3. Click hamburger menu button
+4. Verify menu opens
+5. Verify "Products" link
+6. Verify "Solutions" link</t>
+    </r>
   </si>
   <si>
     <t>1. Mobile view activated
 2. Page loads in mobile view
-3. Banner dismissed
-4. Menu button clicked
-5. Mobile navigation container (#main-menu) present with content
-6. "Products" text in menu
-7. "Solutions" text in menu</t>
+3. Menu button clicked
+4. Mobile navigation container (#main-menu) present with content
+5. "Products" text in menu
+6. "Solutions" text in menu</t>
   </si>
   <si>
     <t>Property</t>
@@ -402,7 +475,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -428,6 +501,18 @@
     <font>
       <b/>
       <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -498,7 +583,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -511,6 +596,9 @@
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
@@ -519,6 +607,9 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
@@ -535,18 +626,30 @@
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="1" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="1" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="1" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="1" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="1" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="1" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="4" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -833,7 +936,7 @@
       <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F2" s="3" t="s">
@@ -842,67 +945,67 @@
       <c r="G2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
     </row>
     <row r="3" ht="99.75" customHeight="1">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-      <c r="V3" s="8"/>
-      <c r="W3" s="8"/>
-      <c r="X3" s="8"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
     </row>
     <row r="4" ht="99.75" customHeight="1">
       <c r="A4" s="3" t="s">
@@ -926,73 +1029,73 @@
       <c r="G4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="5"/>
-      <c r="X4" s="5"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
     </row>
     <row r="5" ht="99.75" customHeight="1">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-      <c r="S5" s="8"/>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="8"/>
-      <c r="W5" s="8"/>
-      <c r="X5" s="8"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="10"/>
     </row>
     <row r="6" ht="99.75" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="13" t="s">
         <v>36</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -1001,76 +1104,76 @@
       <c r="D6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="15" t="s">
         <v>39</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5"/>
-      <c r="T6" s="5"/>
-      <c r="U6" s="5"/>
-      <c r="V6" s="5"/>
-      <c r="W6" s="5"/>
-      <c r="X6" s="5"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="6"/>
+      <c r="U6" s="6"/>
+      <c r="V6" s="6"/>
+      <c r="W6" s="6"/>
+      <c r="X6" s="6"/>
     </row>
     <row r="7" ht="99.75" customHeight="1">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8"/>
-      <c r="X7" s="8"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="10"/>
+      <c r="X7" s="10"/>
     </row>
     <row r="8" ht="99.75" customHeight="1">
       <c r="A8" s="3" t="s">
@@ -1085,7 +1188,7 @@
       <c r="D8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="19" t="s">
         <v>48</v>
       </c>
       <c r="F8" s="3" t="s">
@@ -1094,73 +1197,73 @@
       <c r="G8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
-      <c r="W8" s="5"/>
-      <c r="X8" s="5"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="6"/>
+      <c r="U8" s="6"/>
+      <c r="V8" s="6"/>
+      <c r="W8" s="6"/>
+      <c r="X8" s="6"/>
     </row>
     <row r="9" ht="99.75" customHeight="1">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
-      <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="8"/>
-      <c r="W9" s="8"/>
-      <c r="X9" s="8"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="10"/>
+      <c r="W9" s="10"/>
+      <c r="X9" s="10"/>
     </row>
     <row r="10" ht="99.75" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="4" t="s">
         <v>57</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -1169,76 +1272,76 @@
       <c r="D10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="4" t="s">
         <v>60</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
-      <c r="U10" s="5"/>
-      <c r="V10" s="5"/>
-      <c r="W10" s="5"/>
-      <c r="X10" s="5"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="6"/>
+      <c r="U10" s="6"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="6"/>
+      <c r="X10" s="6"/>
     </row>
     <row r="11" ht="99.75" customHeight="1">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="8"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="8"/>
-      <c r="W11" s="8"/>
-      <c r="X11" s="8"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="10"/>
+      <c r="W11" s="10"/>
+      <c r="X11" s="10"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -2223,12 +2326,14 @@
   </sheetData>
   <autoFilter ref="$A$1:$H$11"/>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="E7"/>
+    <hyperlink r:id="rId1" ref="E6"/>
+    <hyperlink r:id="rId2" ref="E8"/>
+    <hyperlink r:id="rId3" ref="E11"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -2246,130 +2351,130 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15"/>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="21"/>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="21"/>
+      <c r="S1" s="21"/>
+      <c r="T1" s="21"/>
+      <c r="U1" s="21"/>
+      <c r="V1" s="21"/>
+      <c r="W1" s="21"/>
+      <c r="X1" s="21"/>
+      <c r="Y1" s="21"/>
+      <c r="Z1" s="21"/>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="22" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="22" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="22" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="22" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="23" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="23" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="22" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="22" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="22" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="22" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="22" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="22" t="s">
         <v>92</v>
       </c>
     </row>
